--- a/output/xlsx/Settings--GT-.xlsx
+++ b/output/xlsx/Settings--GT-.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Precondition: </t>
   </si>
   <si>
-    <t>Usuario deve estar logado no servidor e extrator como administrador ; Sistema esta configurado para ingles</t>
+    <t>Usuário deve estar logado no servidor e extrator como administrador ; Sistema está configurado para inglês</t>
   </si>
   <si>
     <t>#</t>
@@ -92,19 +92,19 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>administrador: pressiona botao 'Settings'</t>
+    <t>administrador: pressiona botão 'Settings'</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe a janela de configuracoes</t>
-  </si>
-  <si>
-    <t>administrador: seleciona a opção 'Portugues' no campo 'Language' e salva</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe tela inicial 'SAFF extraction' tualizada com todos os campos em portugues</t>
+    <t>SYSTEM exibe a janela de configurações</t>
+  </si>
+  <si>
+    <t>administrador: seleciona a opção 'Português' no campo 'Language' e pressiona botão 'Save'</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe tela inicial 'SAFF extraction' tualizada com todos os campos em português</t>
   </si>
   <si>
     <t xml:space="preserve">Postcondition: </t>
@@ -116,7 +116,7 @@
     <t>Alternative Flow 1: Linguagem Espanhol</t>
   </si>
   <si>
-    <t>administrador: Abre arquivo de configuracoes e modifica propriedade linguagem para 'Espanol', salva e loga novamente no sistema</t>
+    <t>administrador: Abre arquivo de configurações e modifica propriedade linguagem para 'Español', salva e loga novamente no sistema</t>
   </si>
   <si>
     <t>SYSTEM exibe tela inicial 'SAFF extraction' atualizada com todos os campos em espanhol</t>
@@ -128,10 +128,10 @@
     <t>Alternative Flow 2: Visible Test Type</t>
   </si>
   <si>
-    <t>administrador: seleciona somente opcao 'Pre test' no campo 'Visible Test Type' e pressiona botao 'Save'</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza tela inicial 'SAFF extraction' exibindo somente 'Pre test' como opcao de teste.</t>
+    <t>administrador: seleciona somente opção 'Pre test' no campo 'Visible Test Type' e pressiona botão 'Save'</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza tela inicial 'SAFF extraction' exibindo somente 'Pre test' como opção de teste.</t>
   </si>
   <si>
     <t>TC4</t>
@@ -140,10 +140,10 @@
     <t>Alternative Flow 3: Default Test Type</t>
   </si>
   <si>
-    <t>administrador: seleciona somente opcao 'Pre test' no campo 'Default Test Type' e pressiona botao 'Save'</t>
-  </si>
-  <si>
-    <t>SYSTEM atualiza tela inicial 'SAFF extraction' exibindo e tipo de teste 'Pre test' esta marcado.</t>
+    <t>administrador: seleciona somente opção 'Pre test' no campo 'Default Test Type' e pressiona botão 'Save'</t>
+  </si>
+  <si>
+    <t>SYSTEM atualiza tela inicial 'SAFF extraction' exibindo e tipo de teste 'Pre test' está marcado.</t>
   </si>
 </sst>
 </file>

--- a/output/xlsx/Settings--GT-.xlsx
+++ b/output/xlsx/Settings--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="44">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -116,7 +116,7 @@
     <t>Alternative Flow 1: Linguagem Espanhol</t>
   </si>
   <si>
-    <t>administrador: Abre arquivo de configurações e modifica propriedade linguagem para 'Español', salva e loga novamente no sistema</t>
+    <t>administrador: seleciona a opção 'Español' no campo 'Language' e pressiona botão 'Save'</t>
   </si>
   <si>
     <t>SYSTEM exibe tela inicial 'SAFF extraction' atualizada com todos os campos em espanhol</t>
@@ -235,11 +235,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="106.2265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="87.21484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.8984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="76.42578125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -444,228 +444,248 @@
         <v>1.0</v>
       </c>
       <c r="B19" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B20" t="s" s="3">
         <v>34</v>
       </c>
-      <c r="C19" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s" s="3">
+      <c r="C20" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s" s="3">
         <v>35</v>
       </c>
-      <c r="E19" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F19" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="1">
+      <c r="E20" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="1">
         <v>31</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B23" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="C23" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E23" t="s" s="1">
-        <v>14</v>
+      <c r="B21" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="C24" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E24" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B25" t="s" s="0">
+      <c r="B26" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B26" t="s" s="2">
+      <c r="B27" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C26" t="s" s="2">
+      <c r="C27" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D26" t="s" s="2">
+      <c r="D27" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E26" t="s" s="2">
+      <c r="E27" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F26" t="s" s="2">
+      <c r="F27" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B27" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D27" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E27" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B28" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D28" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F28" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n" s="4">
         <v>2.0</v>
       </c>
-      <c r="B28" t="s" s="3">
+      <c r="B29" t="s" s="3">
         <v>38</v>
       </c>
-      <c r="C28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D28" t="s" s="3">
+      <c r="C29" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s" s="3">
         <v>39</v>
       </c>
-      <c r="E28" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F28" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="1">
+      <c r="E29" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F29" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
         <v>31</v>
       </c>
-      <c r="B29" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="C32" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s" s="1">
-        <v>14</v>
+      <c r="B30" t="s" s="0">
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="C33" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E33" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E34" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B34" t="s" s="0">
+      <c r="B35" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
+    <row r="36">
+      <c r="A36" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B35" t="s" s="2">
+      <c r="B36" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="C36" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D35" t="s" s="2">
+      <c r="D36" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E35" t="s" s="2">
+      <c r="E36" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F35" t="s" s="2">
+      <c r="F36" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B36" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F36" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B37" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E37" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F37" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n" s="4">
         <v>2.0</v>
       </c>
-      <c r="B37" t="s" s="3">
+      <c r="B38" t="s" s="3">
         <v>42</v>
       </c>
-      <c r="C37" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s" s="3">
+      <c r="C38" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D38" t="s" s="3">
         <v>43</v>
       </c>
-      <c r="E37" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F37" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="1">
+      <c r="E38" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F38" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
         <v>31</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="B39" t="s" s="0">
         <v>27</v>
       </c>
     </row>
